--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,127 +1024,127 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>345996652.0627705</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>990860.78</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>346023098.6011561</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>4197563.79</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,42 +1309,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4363.115</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-2.42</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025.248</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-14549913.07</v>
+        <v>4197563.79</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,84 +1755,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,275 +1871,275 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>345996652.0627705</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-14549913.07</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>10.57</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>28772</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>346023098.6011561</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-16551504.85</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>5.57</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>10.61</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>80.31</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>28889</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,42 +2302,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2347,32 +2347,32 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-10238853.1</v>
+        <v>-16551504.85</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,32 +2778,32 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-16724214.95</v>
+        <v>-10238853.1</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>879.655</t>
+          <t>925.913</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-37.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>106.08</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-340.77</t>
+          <t>-2115.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-99.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>91028597.0</t>
+          <t>96021508.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>232971461.2</t>
+          <t>172694835.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>285496764.7</t>
+          <t>275104134.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>210141918.6</t>
+          <t>209253045.44</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-52525303</t>
+          <t>-102409298</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16335820.71668774</t>
+          <t>11249661.383083</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6067055.35</v>
+        <v>-16724214.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1845.392</t>
+          <t>879.655</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,37 +3595,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,37 +3635,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>105.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>107.25</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>106.32</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>106.07</t>
+          <t>106.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-173.18</t>
+          <t>-340.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>190867779.0</t>
+          <t>91028597.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>314571614.0</t>
+          <t>232971461.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>294715734.7</t>
+          <t>285496764.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>210060139.96</t>
+          <t>210141918.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>19855879</t>
+          <t>-52525303</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20409070.9113015</t>
+          <t>16335820.71668774</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>9909093.66</v>
+        <v>-6067055.35</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,109 +3895,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1845.392</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-4.67</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>-0.96</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2683.588</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>4.31</t>
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>105.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>107.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>106.33</t>
+          <t>106.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-90.11</t>
+          <t>-173.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-87.42</t>
+          <t>-91.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>278891581.0</t>
+          <t>190867779.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>404032252.8</t>
+          <t>314571614.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>305427884.8</t>
+          <t>294715734.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>208344319.84</t>
+          <t>210060139.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>98604368</t>
+          <t>19855879</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>22318157.68496263</t>
+          <t>20409070.9113015</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>21681212.25</v>
+        <v>9909093.66</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1980.898</t>
+          <t>2683.588</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>26.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>106.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>107.52</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.33</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-90.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-87.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>206664714.0</t>
+          <t>278891581.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>383447545.2</t>
+          <t>404032252.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>308016396.0</t>
+          <t>305427884.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>203968206.38</t>
+          <t>208344319.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>75431149</t>
+          <t>98604368</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>22433965.94514678</t>
+          <t>22318157.68496263</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>28293073.88</v>
+        <v>21681212.25</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3765.047</t>
+          <t>1980.898</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,72 +4772,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-7.22</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24.49</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>107.45</t>
+          <t>107.52</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.01</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.99</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.59</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>397404635.0</t>
+          <t>206664714.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>377513433.2</t>
+          <t>383447545.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>333321756.1</t>
+          <t>308016396.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>201815981.22</t>
+          <t>203968206.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>44191677</t>
+          <t>75431149</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>21368673.59252395</t>
+          <t>22433965.94514678</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>44466716.47</v>
+        <v>28293073.88</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4638.693</t>
+          <t>3765.047</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5203,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-5.69</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13.26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>109.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-10.32</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8.12</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>109.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>107.0</t>
@@ -5283,14 +5283,14 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>-4.59</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>4.31</t>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>109.1</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.45</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.15</t>
+          <t>106.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>-26.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-81.41</t>
+          <t>-82.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>346023098.6011561</t>
+          <t>345996652.0627705</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>499029361.0</t>
+          <t>397404635.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>338022068.2</t>
+          <t>377513433.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>312629274.4</t>
+          <t>333321756.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>196611266.38</t>
+          <t>201815981.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>25392793</t>
+          <t>44191677</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>17169029.43331823</t>
+          <t>21368673.59252395</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>45547403.04</v>
+        <v>44466716.47</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>36349642.99</v>
+        <v>36670902.23</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>33168991.64</v>
+        <v>36349642.99</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>27157338.34</v>
+        <v>33168991.64</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>20693210.76</v>
+        <v>27157338.34</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14.38</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,33 +7453,33 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>20513484.44</v>
+        <v>20693210.76</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1576.875</t>
+          <t>2937.436</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>54.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>100.04</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>94132223.0</t>
+          <t>186975890.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>49651157.8</t>
+          <t>85364570.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29241587.0</t>
+          <t>47098331.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>17093344.86</t>
+          <t>20598389.9</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>20409570</t>
+          <t>38266239</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2320871.669299189</t>
+          <t>5119735.172188113</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>11255095.28</v>
+        <v>20513484.44</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2000.982</t>
+          <t>1576.875</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,74 +8220,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>11.57</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>19.32</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>55.4</t>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>42.51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,190 +8356,190 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>57.02</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>55.61</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>54.09</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>54.93</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>84.31</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-88.44</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>164017250.6796537</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>94132223.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>49651157.8</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>29241587.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>17093344.86</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>20409570</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>2320871.669299189</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>11255095.28</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>56.04</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>55.38</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>54.86</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>50.69</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-90.88</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>163790064.83237</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>117283928.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>33164531.0</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>21175653.4</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>16063082.66</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>11988877</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>696467.3761163405</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>7574393.12</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>101.647</t>
+          <t>2000.982</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,27 +8661,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,33 +8746,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>53.95</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.17999999999999</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.82</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-92.03</t>
+          <t>-90.88</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5619632.0</t>
+          <t>117283928.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>11302095.6</t>
+          <t>33164531.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10580899.1</t>
+          <t>21175653.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>14542103.12</t>
+          <t>16063082.66</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>721196</t>
+          <t>11988877</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-554064.5773030109</t>
+          <t>696467.3761163405</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-434806.69</v>
+        <v>7574393.12</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>415.166</t>
+          <t>101.647</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,195 +9213,195 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>55.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>55.18</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>53.96</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>54.82</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-6.94</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-92.03</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>164017250.6796537</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>5619632.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11302095.6</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>10580899.1</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>14542103.12</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>721196</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-554064.5773030109</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-434806.69</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>55.12</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-14.27</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-91.90</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>163790064.83237</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>22811181.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>11383684.6</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>11689239.5</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>14827950.38</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-305554</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-575747.8300764915</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>103039.83</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>152.919</t>
+          <t>415.166</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.81</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.82</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.51</t>
+          <t>-14.27</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-91.61</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8408825.0</t>
+          <t>22811181.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>8832091.6</t>
+          <t>11383684.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10745680.6</t>
+          <t>11689239.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>14585467.72</t>
+          <t>14827950.38</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1913589</t>
+          <t>-305554</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-699163.7678229639</t>
+          <t>-575747.8300764915</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-974239.6800000001</v>
+        <v>103039.83</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>55.6</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>55.9</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>54.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>211.605</t>
+          <t>152.919</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-17.81</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,42 +10060,42 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -10105,32 +10105,32 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>54.06</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-25.51</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-91.07</t>
+          <t>-91.61</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163790064.83237</t>
+          <t>164017250.6796537</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11699089.0</t>
+          <t>8408825.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>8832016.2</t>
+          <t>8832091.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10806332.8</t>
+          <t>10745680.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>14905401.26</t>
+          <t>14585467.72</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1974316</t>
+          <t>-1913589</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-649149.9653908067</t>
+          <t>-699163.7678229639</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-935306.5600000001</v>
+        <v>-974239.6800000001</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>105.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>105.69</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>253256304.0</t>
+          <t>236949826.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>219688213.02</t>
+          <t>221171326.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>990860.78</v>
+        <v>-3049433.1</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,127 +1455,127 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>345919249.167147</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>990860.78</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>345996652.0627705</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>4197563.79</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-14549913.07</v>
+        <v>4197563.79</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,84 +2186,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-3.76</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-6.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>345919249.167147</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-14549913.07</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>78.19</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>28743</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>345996652.0627705</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-16551504.85</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>10.57</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>28772</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,32 +2778,32 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-10238853.1</v>
+        <v>-16551504.85</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-16724214.95</v>
+        <v>-10238853.1</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>879.655</t>
+          <t>925.913</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-37.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>106.08</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-340.77</t>
+          <t>-2115.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-99.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>91028597.0</t>
+          <t>96021508.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>232971461.2</t>
+          <t>172694835.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>285496764.7</t>
+          <t>275104134.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>210141918.6</t>
+          <t>209253045.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-52525303</t>
+          <t>-102409298</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>16335820.71668774</t>
+          <t>11249661.383083</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6067055.35</v>
+        <v>-16724214.95</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1845.392</t>
+          <t>879.655</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>105.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>107.25</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>106.32</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>106.07</t>
+          <t>106.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-173.18</t>
+          <t>-340.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>190867779.0</t>
+          <t>91028597.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>314571614.0</t>
+          <t>232971461.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>294715734.7</t>
+          <t>285496764.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>210060139.96</t>
+          <t>210141918.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>19855879</t>
+          <t>-52525303</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20409070.9113015</t>
+          <t>16335820.71668774</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>9909093.66</v>
+        <v>-6067055.35</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,109 +4326,109 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1845.392</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-4.78</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>-0.96</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2683.588</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-6.2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>4.31</t>
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>105.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>107.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>106.33</t>
+          <t>106.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-90.11</t>
+          <t>-173.18</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-87.42</t>
+          <t>-91.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>278891581.0</t>
+          <t>190867779.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>404032252.8</t>
+          <t>314571614.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>305427884.8</t>
+          <t>294715734.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>208344319.84</t>
+          <t>210060139.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>98604368</t>
+          <t>19855879</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>22318157.68496263</t>
+          <t>20409070.9113015</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>21681212.25</v>
+        <v>9909093.66</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1980.898</t>
+          <t>2683.588</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>26.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>106.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>107.52</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.33</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-90.11</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-87.42</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>206664714.0</t>
+          <t>278891581.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>383447545.2</t>
+          <t>404032252.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>308016396.0</t>
+          <t>305427884.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>203968206.38</t>
+          <t>208344319.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>75431149</t>
+          <t>98604368</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>22433965.94514678</t>
+          <t>22318157.68496263</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>28293073.88</v>
+        <v>21681212.25</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3765.047</t>
+          <t>1980.898</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,72 +5203,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-7.32</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24.49</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-5.69</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>107.45</t>
+          <t>107.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.01</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.99</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-82.59</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>345996652.0627705</t>
+          <t>345919249.167147</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>397404635.0</t>
+          <t>206664714.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>377513433.2</t>
+          <t>383447545.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>333321756.1</t>
+          <t>308016396.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>201815981.22</t>
+          <t>203968206.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>44191677</t>
+          <t>75431149</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>21368673.59252395</t>
+          <t>22433965.94514678</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>44466716.47</v>
+        <v>28293073.88</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.93</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>196536229.2</t>
+          <t>204266767.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>38471387.22</t>
+          <t>41211816.88</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>36670902.23</v>
+        <v>31051352.89</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>36349642.99</v>
+        <v>36670902.23</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>33168991.64</v>
+        <v>36349642.99</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>27157338.34</v>
+        <v>33168991.64</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>20693210.76</v>
+        <v>27157338.34</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,33 +7884,33 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>20513484.44</v>
+        <v>20693210.76</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1576.875</t>
+          <t>2937.436</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>54.24</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>100.04</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>94132223.0</t>
+          <t>186975890.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>49651157.8</t>
+          <t>85364570.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29241587.0</t>
+          <t>47098331.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>17093344.86</t>
+          <t>20598389.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>20409570</t>
+          <t>38266239</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2320871.669299189</t>
+          <t>5119735.172188113</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>11255095.28</v>
+        <v>20513484.44</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2000.982</t>
+          <t>1576.875</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,74 +8651,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>55.4</t>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>42.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,190 +8787,190 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>57.02</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>55.61</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>54.09</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>54.93</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>84.31</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-88.44</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>164101774.370317</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>94132223.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>49651157.8</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>29241587.0</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>17093344.86</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>20409570</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>2320871.669299189</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>11255095.28</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>56.04</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>55.38</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>54.86</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>50.69</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-90.88</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>164017250.6796537</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>117283928.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>33164531.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>21175653.4</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>16063082.66</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>11988877</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>696467.3761163405</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>7574393.12</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>101.647</t>
+          <t>2000.982</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,22 +9092,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9177,33 +9177,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>53.95</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.17999999999999</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.97</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.82</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.03</t>
+          <t>-90.88</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5619632.0</t>
+          <t>117283928.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>11302095.6</t>
+          <t>33164531.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10580899.1</t>
+          <t>21175653.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>14542103.12</t>
+          <t>16063082.66</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>721196</t>
+          <t>11988877</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-554064.5773030109</t>
+          <t>696467.3761163405</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-434806.69</v>
+        <v>7574393.12</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>415.166</t>
+          <t>101.647</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,195 +9644,195 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>55.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>55.18</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>53.96</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>54.82</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-6.94</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-92.03</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>164101774.370317</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>5619632.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11302095.6</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>10580899.1</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>14542103.12</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>721196</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-554064.5773030109</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-434806.69</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>55.12</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-14.27</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-91.90</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>164017250.6796537</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>22811181.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>11383684.6</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>11689239.5</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>14827950.38</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-305554</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-575747.8300764915</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>103039.83</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>152.919</t>
+          <t>415.166</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.81</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.82</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-25.51</t>
+          <t>-14.27</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-91.61</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>164017250.6796537</t>
+          <t>164101774.370317</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8408825.0</t>
+          <t>22811181.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>8832091.6</t>
+          <t>11383684.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10745680.6</t>
+          <t>11689239.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>14585467.72</t>
+          <t>14827950.38</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1913589</t>
+          <t>-305554</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-699163.7678229639</t>
+          <t>-575747.8300764915</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-974239.6800000001</v>
+        <v>103039.83</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>55.6</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>55.9</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>54.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>105.28</t>
+          <t>104.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.69</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>236949826.2</t>
+          <t>240594220.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>221171326.8</t>
+          <t>221461486.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-3049433.1</v>
+        <v>-9428202.439999999</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>105.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>105.69</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>253256304.0</t>
+          <t>236949826.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>219688213.02</t>
+          <t>221171326.8</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>990860.78</v>
+        <v>-3049433.1</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,127 +1886,127 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>345737700.6841726</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>990860.78</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>345919249.167147</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>4197563.79</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-14549913.07</v>
+        <v>4197563.79</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,84 +2617,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-6.31</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>345737700.6841726</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-14549913.07</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>10.79</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>79.06</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>29386</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>345919249.167147</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-16551504.85</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>10.56</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>78.19</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>28743</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-10238853.1</v>
+        <v>-16551504.85</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,42 +3595,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-16724214.95</v>
+        <v>-10238853.1</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>879.655</t>
+          <t>925.913</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-37.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>106.08</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-340.77</t>
+          <t>-2115.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-99.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>91028597.0</t>
+          <t>96021508.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>232971461.2</t>
+          <t>172694835.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>285496764.7</t>
+          <t>275104134.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>210141918.6</t>
+          <t>209253045.44</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-52525303</t>
+          <t>-102409298</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>16335820.71668774</t>
+          <t>11249661.383083</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6067055.35</v>
+        <v>-16724214.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1845.392</t>
+          <t>879.655</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>105.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>107.25</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>106.32</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>106.07</t>
+          <t>106.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-173.18</t>
+          <t>-340.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>190867779.0</t>
+          <t>91028597.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>314571614.0</t>
+          <t>232971461.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>294715734.7</t>
+          <t>285496764.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>210060139.96</t>
+          <t>210141918.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>19855879</t>
+          <t>-52525303</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20409070.9113015</t>
+          <t>16335820.71668774</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>9909093.66</v>
+        <v>-6067055.35</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,109 +4757,109 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1845.392</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>-0.96</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2683.588</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-6.31</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>4.31</t>
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>105.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>107.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.33</t>
+          <t>106.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-90.11</t>
+          <t>-173.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-87.42</t>
+          <t>-91.22</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>278891581.0</t>
+          <t>190867779.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>404032252.8</t>
+          <t>314571614.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>305427884.8</t>
+          <t>294715734.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>208344319.84</t>
+          <t>210060139.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>98604368</t>
+          <t>19855879</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>22318157.68496263</t>
+          <t>20409070.9113015</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>21681212.25</v>
+        <v>9909093.66</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1980.898</t>
+          <t>2683.588</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>26.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>106.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>107.52</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.33</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-90.11</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-87.42</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>345919249.167147</t>
+          <t>345737700.6841726</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>206664714.0</t>
+          <t>278891581.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>383447545.2</t>
+          <t>404032252.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>308016396.0</t>
+          <t>305427884.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>203968206.38</t>
+          <t>208344319.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>75431149</t>
+          <t>98604368</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>22433965.94514678</t>
+          <t>22318157.68496263</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>28293073.88</v>
+        <v>21681212.25</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>59.93</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55.99</t>
+          <t>56.31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>204266767.4</t>
+          <t>180244870.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>41211816.88</t>
+          <t>42670813.98</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>31051352.89</v>
+        <v>21289870.83</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.93</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>196536229.2</t>
+          <t>204266767.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>38471387.22</t>
+          <t>41211816.88</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>36670902.23</v>
+        <v>31051352.89</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>36349642.99</v>
+        <v>36670902.23</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>33168991.64</v>
+        <v>36349642.99</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>27157338.34</v>
+        <v>33168991.64</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>20693210.76</v>
+        <v>27157338.34</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,33 +8315,33 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>20513484.44</v>
+        <v>20693210.76</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1576.875</t>
+          <t>2937.436</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>54.24</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>100.04</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>94132223.0</t>
+          <t>186975890.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>49651157.8</t>
+          <t>85364570.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29241587.0</t>
+          <t>47098331.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>17093344.86</t>
+          <t>20598389.9</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>20409570</t>
+          <t>38266239</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>2320871.669299189</t>
+          <t>5119735.172188113</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>11255095.28</v>
+        <v>20513484.44</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2000.982</t>
+          <t>1576.875</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,74 +9082,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>12.34</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>11.96</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4.52</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>55.4</t>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>42.51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,192 +9218,192 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>57.02</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>55.61</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>54.09</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>54.93</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>84.31</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-88.44</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>164040687.5266187</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>94132223.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>49651157.8</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>29241587.0</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>17093344.86</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>20409570</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>2320871.669299189</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>11255095.28</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>56.04</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>55.38</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>54.86</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>50.69</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
+      <c r="BS21" t="inlineStr">
         <is>
           <t>4.35</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-90.88</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>164101774.370317</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>117283928.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>33164531.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>21175653.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>16063082.66</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>11988877</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>696467.3761163405</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>7574393.12</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
           <t>3.20</t>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>101.647</t>
+          <t>2000.982</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,22 +9523,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9608,33 +9608,33 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>53.95</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>55.17999999999999</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.97</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.82</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.03</t>
+          <t>-90.88</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>164101774.370317</t>
+          <t>164040687.5266187</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5619632.0</t>
+          <t>117283928.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>11302095.6</t>
+          <t>33164531.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10580899.1</t>
+          <t>21175653.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>14542103.12</t>
+          <t>16063082.66</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>721196</t>
+          <t>11988877</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-554064.5773030109</t>
+          <t>696467.3761163405</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-434806.69</v>
+        <v>7574393.12</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>415.166</t>
+          <t>101.647</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,197 +10075,197 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>55.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>55.18</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>53.96</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>54.82</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-6.94</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-92.03</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>164040687.5266187</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>5619632.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11302095.6</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>10580899.1</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>14542103.12</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>721196</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-554064.5773030109</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-434806.69</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>55.12</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-14.27</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
+      <c r="BS23" t="inlineStr">
         <is>
           <t>4.35</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-91.90</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>164101774.370317</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>22811181.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>11383684.6</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>11689239.5</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>14827950.38</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-305554</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-575747.8300764915</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>103039.83</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
           <t>3.20</t>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,17 +10313,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.44</t>
+          <t>105.23</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>222301963.2</t>
+          <t>162561404.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>220229469.28</t>
+          <t>209197245.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>116900919</v>
+        <v>136094275</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>104.8</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>105.44</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>240594220.2</t>
+          <t>222301963.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>221461486.3</t>
+          <t>220229469.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>146495369</v>
+        <v>116900919</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>105.28</t>
+          <t>104.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.69</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>236949826.2</t>
+          <t>240594220.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>221171326.8</t>
+          <t>221461486.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>194852695</v>
+        <v>146495369</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>105.28</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>105.69</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>253256304.0</t>
+          <t>236949826.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>219688213.02</t>
+          <t>221171326.8</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>218463765</v>
+        <v>194852695</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,132 +2773,132 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>345290092.9218078</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>990860.7805953324</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>218463765</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>345492892.75</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>4197563.793432087</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>434797068</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>208362204</v>
+        <v>434797068</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,27 +3447,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,84 +3514,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-6.09</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.81</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,280 +3630,280 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>345290092.9218078</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-14549913.0737094</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>208362204</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>76.97</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>28626</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>光電業右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>345492892.75</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-16551504.84556478</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>128273399</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>76.68</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>28801</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,42 +4066,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4111,32 +4111,32 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10238853.09658802</t>
+          <t>-16551504.84556478</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>276385084</v>
+        <v>128273399</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,32 +4547,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-16724214.95174307</t>
+          <t>-10238853.09658802</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>96021508</v>
+        <v>276385084</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>879.655</t>
+          <t>925.913</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-37.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.08</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-340.77</t>
+          <t>-2115.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-99.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>91028597.0</t>
+          <t>96021508.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>232971461.2</t>
+          <t>172694835.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>285496764.7</t>
+          <t>275104134.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>210141918.6</t>
+          <t>209253045.44</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-52525303</t>
+          <t>-102409298</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16335820.71668774</t>
+          <t>11249661.383083</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6067055.353687972</t>
+          <t>-16724214.95174307</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>91028597</v>
+        <v>96021508</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1845.392</t>
+          <t>879.655</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,37 +5374,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,37 +5414,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>105.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>107.25</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>106.32</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.07</t>
+          <t>106.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-173.18</t>
+          <t>-340.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>345492892.75</t>
+          <t>345290092.9218078</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>190867779.0</t>
+          <t>91028597.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>314571614.0</t>
+          <t>232971461.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>294715734.7</t>
+          <t>285496764.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>210060139.96</t>
+          <t>210141918.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>19855879</t>
+          <t>-52525303</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20409070.9113015</t>
+          <t>16335820.71668774</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9909093.656165302</t>
+          <t>-6067055.353687972</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>190867779</v>
+        <v>91028597</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,17 +5627,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業平上市</t>
+          <t>光電業右下上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.91</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>149719715.0</t>
+          <t>115240085.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>44057108.44</t>
+          <t>44737206.8</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>77457284</v>
+        <v>55041164</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,147 +6246,147 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>163855129.846485</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>149719715.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>44057108.44</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>77457284</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>163971930.6853448</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>81097612</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG14" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>59.93</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>55.99</t>
+          <t>56.31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>204266767.4</t>
+          <t>180244870.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>41211816.88</t>
+          <t>42670813.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>148451128</v>
+        <v>81097612</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.93</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>196536229.2</t>
+          <t>204266767.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>38471387.22</t>
+          <t>41211816.88</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>214153238</v>
+        <v>148451128</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>227439313</v>
+        <v>214153238</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>230083062</v>
+        <v>227439313</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>27157338.34388511</t>
+          <t>33168991.64294642</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>201207096</v>
+        <v>230083062</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>20693210.76151591</t>
+          <t>27157338.34388511</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>109798437</v>
+        <v>201207096</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,33 +9277,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>20513484.4380772</t>
+          <t>20693210.76151591</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>186975890</v>
+        <v>109798437</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1576.875</t>
+          <t>2937.436</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>54.24</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>100.04</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163971930.6853448</t>
+          <t>163855129.846485</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>94132223.0</t>
+          <t>186975890.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>49651157.8</t>
+          <t>85364570.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29241587.0</t>
+          <t>47098331.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>17093344.86</t>
+          <t>20598389.9</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>20409570</t>
+          <t>38266239</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>2320871.669299189</t>
+          <t>5119735.172188113</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>11255095.28180485</t>
+          <t>20513484.4380772</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>94132223</v>
+        <v>186975890</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2000.982</t>
+          <t>1576.875</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,74 +10054,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10.39</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>55.4</t>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>42.51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,195 +10190,195 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>57.02</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>55.61</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>54.09</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>54.93</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>84.31</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-88.44</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>163855129.846485</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>94132223.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>49651157.8</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>29241587.0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>17093344.86</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>20409570</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>2320871.669299189</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>11255095.28180485</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>94132223</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>56.04</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>55.38</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>54.86</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>50.69</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-90.88</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>163971930.6853448</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>117283928.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>33164531.0</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>21175653.4</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>16063082.66</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>11988877</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>696467.3761163405</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>7574393.119922772</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>117283928</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.23</t>
+          <t>105.06</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>162561404.6</t>
+          <t>134482037.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>209197245.52</t>
+          <t>205225010.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>136094275</v>
+        <v>78066930</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.44</t>
+          <t>105.23</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>222301963.2</t>
+          <t>162561404.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>220229469.28</t>
+          <t>209197245.52</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>116900919</v>
+        <v>136094275</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>104.8</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>105.44</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>240594220.2</t>
+          <t>222301963.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>221461486.3</t>
+          <t>220229469.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>146495369</v>
+        <v>116900919</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>105.28</t>
+          <t>104.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.69</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>236949826.2</t>
+          <t>240594220.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>221171326.8</t>
+          <t>221461486.3</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>194852695</v>
+        <v>146495369</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>105.28</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>105.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>253256304.0</t>
+          <t>236949826.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>219688213.02</t>
+          <t>221171326.8</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>218463765</v>
+        <v>194852695</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,132 +3209,132 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>344963173.5838109</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>990860.7805953324</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>218463765</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>345290092.9218078</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>4197563.793432087</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>434797068</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,27 +3447,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>208362204</v>
+        <v>434797068</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,84 +3950,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6.74</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,280 +4066,280 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>344963173.5838109</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-14549913.0737094</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>208362204</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>78.34</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>29094</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>345290092.9218078</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-16551504.84556478</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>128273399</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>76.97</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>28626</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>光電業右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,32 +4547,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-10238853.09658802</t>
+          <t>-16551504.84556478</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>276385084</v>
+        <v>128273399</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,32 +4983,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-16724214.95174307</t>
+          <t>-10238853.09658802</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>96021508</v>
+        <v>276385084</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>879.655</t>
+          <t>925.913</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-37.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>785</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>106.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.08</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-340.77</t>
+          <t>-2115.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-99.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>345290092.9218078</t>
+          <t>344963173.5838109</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>91028597.0</t>
+          <t>96021508.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>232971461.2</t>
+          <t>172694835.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>285496764.7</t>
+          <t>275104134.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>210141918.6</t>
+          <t>209253045.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-52525303</t>
+          <t>-102409298</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16335820.71668774</t>
+          <t>11249661.383083</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6067055.353687972</t>
+          <t>-16724214.95174307</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>91028597</v>
+        <v>96021508</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,17 +5627,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>57.23</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>115240085.2</t>
+          <t>84222262.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>44737206.8</t>
+          <t>45652449.62</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>55041164</v>
+        <v>59064123</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>149719715.0</t>
+          <t>115240085.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>44057108.44</t>
+          <t>44737206.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>77457284</v>
+        <v>55041164</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,147 +6682,147 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>163747309.0078797</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>149719715.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>44057108.44</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>77457284</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>163855129.846485</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>81097612</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG15" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>59.93</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>55.99</t>
+          <t>56.31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>204266767.4</t>
+          <t>180244870.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>41211816.88</t>
+          <t>42670813.98</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>148451128</v>
+        <v>81097612</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.93</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>196536229.2</t>
+          <t>204266767.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>38471387.22</t>
+          <t>41211816.88</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>214153238</v>
+        <v>148451128</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>227439313</v>
+        <v>214153238</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>230083062</v>
+        <v>227439313</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>27157338.34388511</t>
+          <t>33168991.64294642</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>201207096</v>
+        <v>230083062</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>20693210.76151591</t>
+          <t>27157338.34388511</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>109798437</v>
+        <v>201207096</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,33 +9713,33 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>20513484.4380772</t>
+          <t>20693210.76151591</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>186975890</v>
+        <v>109798437</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1576.875</t>
+          <t>2937.436</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>874</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>54.24</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>100.04</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163855129.846485</t>
+          <t>163747309.0078797</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>94132223.0</t>
+          <t>186975890.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>49651157.8</t>
+          <t>85364570.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29241587.0</t>
+          <t>47098331.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>17093344.86</t>
+          <t>20598389.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>20409570</t>
+          <t>38266239</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>2320871.669299189</t>
+          <t>5119735.172188113</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>11255095.28180485</t>
+          <t>20513484.4380772</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>94132223</v>
+        <v>186975890</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,37 +1054,37 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.82</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.06</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>134482037.6</t>
+          <t>116147614.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>205225010.12</t>
+          <t>201428975.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>78066930</v>
+        <v>103180579</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.23</t>
+          <t>105.06</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>162561404.6</t>
+          <t>134482037.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>209197245.52</t>
+          <t>205225010.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>136094275</v>
+        <v>78066930</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.44</t>
+          <t>105.23</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>222301963.2</t>
+          <t>162561404.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>220229469.28</t>
+          <t>209197245.52</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>116900919</v>
+        <v>136094275</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>104.8</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>105.44</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>240594220.2</t>
+          <t>222301963.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>221461486.3</t>
+          <t>220229469.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>146495369</v>
+        <v>116900919</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>105.28</t>
+          <t>104.8</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.69</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>236949826.2</t>
+          <t>240594220.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>221171326.8</t>
+          <t>221461486.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>194852695</v>
+        <v>146495369</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>105.28</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>105.69</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>253256304.0</t>
+          <t>236949826.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>219688213.02</t>
+          <t>221171326.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>218463765</v>
+        <v>194852695</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,132 +3645,132 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>105.84</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>105.8</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-118.58</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>344691081.5879828</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>253256304.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>212975569.9</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>219688213.02</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>40280734</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1625660.58438845</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>990860.7805953324</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>218463765</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>105.9</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-144.56</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-112.44</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>344963173.5838109</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>434797068.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>230869656.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-2101804</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>1741078.730532653</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>4197563.793432087</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>434797068</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/16</t>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>160014158.4</t>
+          <t>228767852.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>210329621.68</t>
+          <t>217695178.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>208362204</v>
+        <v>434797068</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,84 +4386,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-5.03</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.24</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,280 +4502,280 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>106.6</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>106.11</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>344691081.5879828</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>160014158.4</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>210329621.68</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-14549913.0737094</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>208362204</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>10.85</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>79.73</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>29532</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>344963173.5838109</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-16551504.84556478</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>128273399</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>5.53</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>10.69</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>78.34</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>29094</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,32 +4983,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>106.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106.24</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>186638909.8</t>
+          <t>156515273.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>208948816.74</t>
+          <t>208482988.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-10238853.09658802</t>
+          <t>-16551504.84556478</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>276385084</v>
+        <v>128273399</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>925.913</t>
+          <t>2605.041</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,42 +5374,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>106.8</t>
+          <t>106.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>106.28</t>
+          <t>106.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>106.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2115.09</t>
+          <t>-534.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.25</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>344963173.5838109</t>
+          <t>344691081.5879828</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>96021508.0</t>
+          <t>276385084.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>172694835.8</t>
+          <t>186638909.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>275104134.5</t>
+          <t>285043227.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>209253045.44</t>
+          <t>208948816.74</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-102409298</t>
+          <t>-98404317</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>11249661.383083</t>
+          <t>7943736.078518227</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-16724214.95174307</t>
+          <t>-10238853.09658802</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>96021508</v>
+        <v>276385084</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,72 +5810,72 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>57.23</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>84222262.2</t>
+          <t>68193204.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>45652449.62</t>
+          <t>46606279.72</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>59064123</v>
+        <v>68305837</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>57.23</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>115240085.2</t>
+          <t>84222262.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>44737206.8</t>
+          <t>45652449.62</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>55041164</v>
+        <v>59064123</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.91</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>149719715.0</t>
+          <t>115240085.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>44057108.44</t>
+          <t>44737206.8</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>77457284</v>
+        <v>55041164</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,147 +7118,147 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>163659628.6738198</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>149719715.0</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>44057108.44</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>77457284</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>163747309.0078797</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>81097612</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG16" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>59.93</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>55.99</t>
+          <t>56.31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>204266767.4</t>
+          <t>180244870.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>41211816.88</t>
+          <t>42670813.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>148451128</v>
+        <v>81097612</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.93</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.99</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>196536229.2</t>
+          <t>204266767.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>38471387.22</t>
+          <t>41211816.88</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>214153238</v>
+        <v>148451128</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>58.69</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>191100759.6</t>
+          <t>196536229.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>34338500.78</t>
+          <t>38471387.22</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>227439313</v>
+        <v>214153238</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>58.69</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>164439341.6</t>
+          <t>191100759.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>30095348.66</t>
+          <t>34338500.78</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>230083062</v>
+        <v>227439313</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>141879514.8</t>
+          <t>164439341.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>26134633.24</t>
+          <t>30095348.66</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>27157338.34388511</t>
+          <t>33168991.64294642</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>201207096</v>
+        <v>230083062</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>102762022.0</t>
+          <t>141879514.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>22355997.5</t>
+          <t>26134633.24</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>20693210.76151591</t>
+          <t>27157338.34388511</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>109798437</v>
+        <v>201207096</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2937.436</t>
+          <t>1723.463</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,33 +10149,33 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>60.27999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.46</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>100.04</t>
+          <t>98.82</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163747309.0078797</t>
+          <t>163659628.6738198</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>186975890.0</t>
+          <t>109798437.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>85364570.8</t>
+          <t>102762022.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>47098331.2</t>
+          <t>57072853.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>20598389.9</t>
+          <t>22355997.5</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>38266239</t>
+          <t>45689168</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>5119735.172188113</t>
+          <t>7515654.493623158</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>20513484.4380772</t>
+          <t>20693210.76151591</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>186975890</v>
+        <v>109798437</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>105</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>103180579</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>78066930</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>136094275</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>116900919</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>146495369</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>194852695</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>218463765</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>434797068</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>208362204</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>128273399</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>276385084</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>67.44000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>57.54</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>68305837.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>68193204.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>68193204</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>136229985.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>46606279.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>46606279.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1579885.667524114</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>68305837</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>68305837.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>67.64000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>59064123.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>84222262.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>84222262.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>140379245.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>45652449.62</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>45652449.62</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1268393.578065202</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>59064123</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>59064123.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>56.91</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>55041164.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>115240085.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>115240085.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>153170422.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>44737206.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>44737206.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>6282247.801119044</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>55041164</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>55041164.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>68.92</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>56.6</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>77457284.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>149719715.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>149719715</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>157079528.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>44057108.44</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>44057108.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>13651562.01972742</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>77457284</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>69.28</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>60.56</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>56.31</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>56.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>81097612.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>180244870.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>161062192.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>42670813.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>21289870.83132054</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>81097612</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>81097612.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>69.06</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55.99</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>148451128.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>204266767.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>204266767.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>153514394.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>41211816.88</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>41211816.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>31051352.88962071</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>148451128</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>148451128.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>68.47999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>214153238.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>196536229.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>196536229.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>140950400.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>38471387.22</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>38471387.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>36670902.22684878</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>214153238</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>214153238.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>67.32000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>58.69</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>227439313.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>191100759.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>191100759.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>120375958.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>34338500.78</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>34338500.78</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>36349642.98621568</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>227439313</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>227439313.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>64.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>54.98</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>54.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>230083062.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>164439341.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>164439341.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>98801936.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>30095348.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>30095348.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>33168991.64294642</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>230083062</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>230083062.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>62.72000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>54.65</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>201207096.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>141879514.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>141879514.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>76590805.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>26134633.24</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>26134633.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>27157338.34388511</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>201207096</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>201207096.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>60.27999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>56.46</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>109798437.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>102762022.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>102762022</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>57072853.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>22355997.5</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>22355997.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>20693210.76151591</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>109798437</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>109798437.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>105.81</v>
+        <v>105.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.84</v>
+        <v>105.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>253256304</v>
+        <v>236949826.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>219688213.02</v>
+        <v>221171326.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>106.24</v>
+        <v>105.81</v>
       </c>
       <c r="AN9" t="n">
-        <v>106</v>
+        <v>105.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.9</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-144.56</t>
+          <t>-118.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>228767852.6</v>
+        <v>253256304</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>230869656.9</t>
+          <t>212975569.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>217695178.8</v>
+        <v>219688213.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2101804</t>
+          <t>40280734</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1741078.730532653</t>
+          <t>1625660.58438845</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>4197563.793432087</t>
+          <t>990860.7805953324</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>106.6</v>
+        <v>106.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>106.11</v>
+        <v>106</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>160014158.4</v>
+        <v>228767852.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>210329621.68</v>
+        <v>217695178.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,92 +4768,92 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.47</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,274 +4884,274 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>344460602.4792857</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>160014158.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>210329621.68</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-14549913.0737094</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>11.01</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>80.32</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>29971</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM11" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>106.18</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>344691081.5879828</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>156515273.4</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>208482988.26</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-16551504.84556478</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>5.45</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>79.73</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>29532</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2605.041</t>
+          <t>1226.919</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-44.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,42 +5314,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5358,29 +5358,29 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>106.85</v>
+        <v>106.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>106.24</v>
+        <v>106.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>106.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-534.87</t>
+          <t>-214.36</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>344691081.5879828</t>
+          <t>344460602.4792857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>186638909.8</v>
+        <v>156515273.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>285043227.5</t>
+          <t>280273763.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>208948816.74</v>
+        <v>208482988.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-98404317</t>
+          <t>-123758489</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7943736.078518227</t>
+          <t>4175237.474813148</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-10238853.09658802</t>
+          <t>-16551504.84556478</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>276385084.0</t>
+          <t>128273399.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>104.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>105.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>價_量;【b】</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN16" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,141 +7464,141 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>60.56</v>
+        <v>61.16</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.31</v>
+        <v>56.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>163538310.1864286</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>149719715</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>44057108.44</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>163659628.6738198</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>180244870.6</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>42670813.98</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG17" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>59.93</v>
+        <v>60.56</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.99</v>
+        <v>56.31</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>204266767.4</v>
+        <v>180244870.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>41211816.88</v>
+        <v>42670813.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>59.37</v>
+        <v>59.93</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.7</v>
+        <v>55.99</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>196536229.2</v>
+        <v>204266767.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>38471387.22</v>
+        <v>41211816.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>58.69</v>
+        <v>59.37</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.39</v>
+        <v>55.7</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>191100759.6</v>
+        <v>196536229.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>34338500.78</v>
+        <v>38471387.22</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>57.81</v>
+        <v>58.69</v>
       </c>
       <c r="AN21" t="n">
-        <v>54.98</v>
+        <v>55.39</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>164439341.6</v>
+        <v>191100759.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>30095348.66</v>
+        <v>34338500.78</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.11</v>
+        <v>57.81</v>
       </c>
       <c r="AN22" t="n">
-        <v>54.65</v>
+        <v>54.98</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>141879514.8</v>
+        <v>164439341.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>26134633.24</v>
+        <v>30095348.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>27157338.34388511</t>
+          <t>33168991.64294642</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1723.463</t>
+          <t>3030.648</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>81.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>60.27999999999999</t>
+          <t>62.72000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56.46</v>
+        <v>57.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>54.4</v>
+        <v>54.65</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>98.82</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-72.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163659628.6738198</t>
+          <t>163538310.1864286</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>102762022</v>
+        <v>141879514.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>57072853.3</t>
+          <t>76590805.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>22355997.5</v>
+        <v>26134633.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>45689168</t>
+          <t>65288709</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>7515654.493623158</t>
+          <t>10537452.00904807</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>20693210.76151591</t>
+          <t>27157338.34388511</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>109798437.0</t>
+          <t>201207096.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,32 +1449,32 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN3" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN4" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>105.81</v>
+        <v>105.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.84</v>
+        <v>105.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>253256304</v>
+        <v>236949826.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>219688213.02</v>
+        <v>221171326.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>106.24</v>
+        <v>105.81</v>
       </c>
       <c r="AN10" t="n">
-        <v>106</v>
+        <v>105.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.9</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-144.56</t>
+          <t>-118.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>228767852.6</v>
+        <v>253256304</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>230869656.9</t>
+          <t>212975569.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>217695178.8</v>
+        <v>219688213.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2101804</t>
+          <t>40280734</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1741078.730532653</t>
+          <t>1625660.58438845</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>4197563.793432087</t>
+          <t>990860.7805953324</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>106.6</v>
+        <v>106.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>106.11</v>
+        <v>106</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>344460602.4792857</t>
+          <t>344090050.4828816</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>160014158.4</v>
+        <v>228767852.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>210329621.68</v>
+        <v>217695178.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1226.919</t>
+          <t>2025.248</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,92 +5198,92 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.57</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-32.57</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-44.16</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,269 +5319,269 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>551</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>103.8</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>105.98</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-157.39</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-107.94</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>344090050.4828816</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>160014158.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>237292886.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>210329621.68</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-77278727</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>1294445.082732756</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-14549913.0737094</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-11.06846749116489</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>5.933446073116056</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>12.2962952682113</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>11.01</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>80.72</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>29971</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>台表科-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>光電業平上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM12" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>106.18</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>106.02</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-214.36</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-104.82</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>344460602.4792857</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>156515273.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>280273763.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>208482988.26</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-123758489</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>4175237.474813148</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-16551504.84556478</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>128273399.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-11.06846749116489</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>5.933446073116056</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>12.2962952682113</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>12.67%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>7.38%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>80.32</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>29971</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>台表科-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>光電業平上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>800.087</t>
+          <t>484.079</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,211 +5749,211 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>63.52</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.84</v>
+        <v>58.15</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.89</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-28.19</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>163373472.149786</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>53378696</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>101549205.5</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>48028060.24</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-48170509</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>7502748.728116079</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-8338053.473961905</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-26.41</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>163538310.1864286</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>62471906.6</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>121358388.6</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>47556857.96</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-58886481</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>10382894.58303935</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-4720287.39774853</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
           <t>11.78</t>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,136 +7899,136 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>60.56</v>
+        <v>61.16</v>
       </c>
       <c r="AN18" t="n">
-        <v>56.31</v>
+        <v>56.6</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>163373472.149786</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>149719715</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>44057108.44</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>163538310.1864286</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>180244870.6</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>42670813.98</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG18" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>59.93</v>
+        <v>60.56</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.99</v>
+        <v>56.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>204266767.4</v>
+        <v>180244870.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>41211816.88</v>
+        <v>42670813.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>59.37</v>
+        <v>59.93</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.7</v>
+        <v>55.99</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>196536229.2</v>
+        <v>204266767.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>38471387.22</v>
+        <v>41211816.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>58.69</v>
+        <v>59.37</v>
       </c>
       <c r="AN21" t="n">
-        <v>55.39</v>
+        <v>55.7</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>191100759.6</v>
+        <v>196536229.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>34338500.78</v>
+        <v>38471387.22</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.81</v>
+        <v>58.69</v>
       </c>
       <c r="AN22" t="n">
-        <v>54.98</v>
+        <v>55.39</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>164439341.6</v>
+        <v>191100759.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>30095348.66</v>
+        <v>34338500.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3030.648</t>
+          <t>3323.878</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>81.71</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>62.72000000000001</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.11</v>
+        <v>57.81</v>
       </c>
       <c r="AN23" t="n">
-        <v>54.65</v>
+        <v>54.98</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-72.63</t>
+          <t>-64.46</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163538310.1864286</t>
+          <t>163373472.149786</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>141879514.8</v>
+        <v>164439341.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>76590805.2</t>
+          <t>98801936.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>26134633.24</v>
+        <v>30095348.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>65288709</t>
+          <t>65637405</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>10537452.00904807</t>
+          <t>14019227.33734013</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>27157338.34388511</t>
+          <t>33168991.64294642</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>201207096.0</t>
+          <t>230083062.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,107 +883,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1520.716</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>550.832</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-22.34</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.57</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-38.29</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.87</t>
+          <t>96.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>100.68</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>102.14</v>
+        <v>101.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.91</v>
+        <v>104.86</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.22</t>
+          <t>105.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.87</t>
+          <t>-137.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>99209604.59999999</v>
+        <v>103202924</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>160755783.9</t>
+          <t>132882164.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>200342843.58</v>
+        <v>201053456.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-61546179</t>
+          <t>-29679240</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-15506725.825092</t>
+          <t>-16632799.68084102</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-28477904.92889903</t>
+          <t>-22826205.88746065</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>102.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>105.81</v>
+        <v>105.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.84</v>
+        <v>105.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>253256304</v>
+        <v>236949826.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>219688213.02</v>
+        <v>221171326.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>106.24</v>
+        <v>105.81</v>
       </c>
       <c r="AN11" t="n">
-        <v>106</v>
+        <v>105.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.9</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-144.56</t>
+          <t>-118.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>228767852.6</v>
+        <v>253256304</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>230869656.9</t>
+          <t>212975569.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>217695178.8</v>
+        <v>219688213.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2101804</t>
+          <t>40280734</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1741078.730532653</t>
+          <t>1625660.58438845</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>4197563.793432087</t>
+          <t>990860.7805953324</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025.248</t>
+          <t>4363.115</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>102.86</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>106.6</v>
+        <v>106.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>106.11</v>
+        <v>106</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>105.98</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-157.39</t>
+          <t>-144.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>344090050.4828816</t>
+          <t>343933357.1175214</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>160014158.4</v>
+        <v>228767852.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>237292886.2</t>
+          <t>230869656.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>210329621.68</v>
+        <v>217695178.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-77278727</t>
+          <t>-2101804</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1294445.082732756</t>
+          <t>1741078.730532653</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-14549913.0737094</t>
+          <t>4197563.793432087</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>208362204.0</t>
+          <t>434797068.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>價_量;【c】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,107 +5613,107 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>486.403</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>484.079</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-40.56</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-2.89</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-47.44</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>64.09999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.15</v>
+        <v>58.44</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-28.19</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>53378696</v>
+        <v>48728972.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>101549205.5</t>
+          <t>81984528.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>48028060.24</v>
+        <v>48567572.86</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-48170509</t>
+          <t>-33255556</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>7502748.728116079</t>
+          <t>4705873.575257879</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-8338053.473961905</t>
+          <t>-10676939.76546222</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>800.087</t>
+          <t>484.079</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,219 +6174,219 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>63.52</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.84</v>
+        <v>58.15</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.89</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-28.19</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>163208679.1965812</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>53378696</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>101549205.5</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>48028060.24</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-48170509</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>7502748.728116079</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-8338053.473961905</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-26.41</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>163373472.149786</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>62471906.6</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>121358388.6</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>47556857.96</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-58886481</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>10382894.58303935</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-4720287.39774853</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6456,14 +6456,14 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN18" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,141 +8324,141 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>60.56</v>
+        <v>61.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>56.31</v>
+        <v>56.6</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>163208679.1965812</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>149719715</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>44057108.44</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>163373472.149786</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>180244870.6</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>42670813.98</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG19" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>59.93</v>
+        <v>60.56</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.99</v>
+        <v>56.31</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>204266767.4</v>
+        <v>180244870.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41211816.88</v>
+        <v>42670813.98</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>59.37</v>
+        <v>59.93</v>
       </c>
       <c r="AN21" t="n">
-        <v>55.7</v>
+        <v>55.99</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>196536229.2</v>
+        <v>204266767.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>38471387.22</v>
+        <v>41211816.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>58.69</v>
+        <v>59.37</v>
       </c>
       <c r="AN22" t="n">
-        <v>55.39</v>
+        <v>55.7</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>191100759.6</v>
+        <v>196536229.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>34338500.78</v>
+        <v>38471387.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3323.878</t>
+          <t>3155.256</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.32000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.81</v>
+        <v>58.69</v>
       </c>
       <c r="AN23" t="n">
-        <v>54.98</v>
+        <v>55.39</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>55.69</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-54.64</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163373472.149786</t>
+          <t>163208679.1965812</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>164439341.6</v>
+        <v>191100759.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>98801936.3</t>
+          <t>120375958.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30095348.66</v>
+        <v>34338500.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>65637405</t>
+          <t>70724800</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>14019227.33734013</t>
+          <t>17454675.8987056</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>33168991.64294642</t>
+          <t>36349642.98621568</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>230083062.0</t>
+          <t>227439313.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1520.716</t>
+          <t>1181.443</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.8</v>
+        <v>101.74</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.86</v>
+        <v>104.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.12</t>
+          <t>105.04</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.11</t>
+          <t>-134.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>103202924</v>
+        <v>111924097.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>132882164.3</t>
+          <t>123203067.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>201053456.9</v>
+        <v>200134642.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29679240</t>
+          <t>-11278970</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16632799.68084102</t>
+          <t>-17285979.26244506</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-22826205.88746065</t>
+          <t>-20878466.96126726</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>550.832</t>
+          <t>1520.716</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.29</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.87</t>
+          <t>96.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>100.68</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>102.14</v>
+        <v>101.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>104.91</v>
+        <v>104.86</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.22</t>
+          <t>105.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.87</t>
+          <t>-137.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>99209604.59999999</v>
+        <v>103202924</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>160755783.9</t>
+          <t>132882164.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>200342843.58</v>
+        <v>201053456.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-61546179</t>
+          <t>-29679240</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-15506725.825092</t>
+          <t>-16632799.68084102</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-28477904.92889903</t>
+          <t>-22826205.88746065</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>102.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,32 +2309,32 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN5" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,32 +2739,32 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>105.81</v>
+        <v>105.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.84</v>
+        <v>105.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>253256304</v>
+        <v>236949826.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>219688213.02</v>
+        <v>221171326.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4363.115</t>
+          <t>2216.824</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>101.84</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>106.24</v>
+        <v>105.81</v>
       </c>
       <c r="AN12" t="n">
-        <v>106</v>
+        <v>105.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>105.9</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-144.56</t>
+          <t>-118.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>343933357.1175214</t>
+          <t>343703735.2681366</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>228767852.6</v>
+        <v>253256304</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>230869656.9</t>
+          <t>212975569.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>217695178.8</v>
+        <v>219688213.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2101804</t>
+          <t>40280734</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1741078.730532653</t>
+          <t>1625660.58438845</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>4197563.793432087</t>
+          <t>990860.7805953324</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>434797068.0</t>
+          <t>218463765.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>486.403</t>
+          <t>1059.506</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-24.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.08</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>64.58</v>
+        <v>65.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.44</v>
+        <v>58.76</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.22</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.99</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-30.95</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>48728972.4</v>
+        <v>51050573.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>81984528.8</t>
+          <t>67636417.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>48567572.86</v>
+        <v>49798402.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-33255556</t>
+          <t>-16585844</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4705873.575257879</t>
+          <t>2577082.57131422</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-10676939.76546222</t>
+          <t>-9131267.9503759</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>19.40</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>484.079</t>
+          <t>486.403</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,92 +6058,92 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-40.56</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-47.44</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,17 +6174,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>64.09999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.15</v>
+        <v>58.44</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-28.19</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>53378696</v>
+        <v>48728972.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>101549205.5</t>
+          <t>81984528.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>48028060.24</v>
+        <v>48567572.86</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-48170509</t>
+          <t>-33255556</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>7502748.728116079</t>
+          <t>4705873.575257879</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-8338053.473961905</t>
+          <t>-10676939.76546222</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>800.087</t>
+          <t>484.079</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,219 +6604,219 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>63.52</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.84</v>
+        <v>58.15</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.89</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-28.19</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>163127312.9295875</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>53378696</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>101549205.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>48028060.24</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-48170509</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>7502748.728116079</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-8338053.473961905</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-26.41</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>163208679.1965812</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>62471906.6</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>121358388.6</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>47556857.96</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-58886481</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>10382894.58303935</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-4720287.39774853</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>4.62</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN16" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,68 +7464,68 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN19" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,141 +8754,141 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>60.56</v>
+        <v>61.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.31</v>
+        <v>56.6</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>163127312.9295875</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>149719715</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>44057108.44</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>163208679.1965812</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>180244870.6</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>42670813.98</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG20" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>59.93</v>
+        <v>60.56</v>
       </c>
       <c r="AN21" t="n">
-        <v>55.99</v>
+        <v>56.31</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>204266767.4</v>
+        <v>180244870.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>41211816.88</v>
+        <v>42670813.98</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>59.37</v>
+        <v>59.93</v>
       </c>
       <c r="AN22" t="n">
-        <v>55.7</v>
+        <v>55.99</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>196536229.2</v>
+        <v>204266767.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>38471387.22</v>
+        <v>41211816.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3155.256</t>
+          <t>3083.64</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>85.07</t>
+          <t>83.14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>67.32000000000001</t>
+          <t>68.47999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>58.69</v>
+        <v>59.37</v>
       </c>
       <c r="AN23" t="n">
-        <v>55.39</v>
+        <v>55.7</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.69</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-46.13</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163208679.1965812</t>
+          <t>163127312.9295875</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>191100759.6</v>
+        <v>196536229.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>120375958.7</t>
+          <t>140950400.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>34338500.78</v>
+        <v>38471387.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>70724800</t>
+          <t>55585829</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>17454675.8987056</t>
+          <t>20411018.41072763</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>36349642.98621568</t>
+          <t>36670902.22684878</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>227439313.0</t>
+          <t>214153238.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1181.443</t>
+          <t>646.583</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.74</v>
+        <v>101.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.83</v>
+        <v>104.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>105.04</t>
+          <t>104.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.64</t>
+          <t>-131.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>111924097.6</v>
+        <v>104630422.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>123203067.6</t>
+          <t>110389018.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>200134642.08</v>
+        <v>197447365.46</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-11278970</t>
+          <t>-5758596</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17285979.26244506</t>
+          <t>-18182772.10497662</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-20878466.96126726</t>
+          <t>-23115132.73890021</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1520.716</t>
+          <t>1181.443</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.8</v>
+        <v>101.74</v>
       </c>
       <c r="AN3" t="n">
-        <v>104.86</v>
+        <v>104.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.12</t>
+          <t>105.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.11</t>
+          <t>-134.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>103202924</v>
+        <v>111924097.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>132882164.3</t>
+          <t>123203067.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>201053456.9</v>
+        <v>200134642.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29679240</t>
+          <t>-11278970</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16632799.68084102</t>
+          <t>-17285979.26244506</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-22826205.88746065</t>
+          <t>-20878466.96126726</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>550.832</t>
+          <t>1520.716</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.29</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.87</t>
+          <t>96.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.68</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>102.14</v>
+        <v>101.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>104.91</v>
+        <v>104.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.22</t>
+          <t>105.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.87</t>
+          <t>-137.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>99209604.59999999</v>
+        <v>103202924</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>160755783.9</t>
+          <t>132882164.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>200342843.58</v>
+        <v>201053456.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-61546179</t>
+          <t>-29679240</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-15506725.825092</t>
+          <t>-16632799.68084102</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-28477904.92889903</t>
+          <t>-22826205.88746065</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>102.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2734,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN6" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,33 +3204,33 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2216.824</t>
+          <t>1985.218</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>647</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>101.84</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>105.81</v>
+        <v>105.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>105.84</v>
+        <v>105.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-118.58</t>
+          <t>-94.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-123.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>343703735.2681366</t>
+          <t>343357662.2109375</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>253256304</v>
+        <v>236949826.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>212975569.9</t>
+          <t>211794368.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>219688213.02</v>
+        <v>221171326.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>40280734</t>
+          <t>25155458</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1625660.58438845</t>
+          <t>906415.4024971072</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>990860.7805953324</t>
+          <t>-3049433.097905278</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>218463765.0</t>
+          <t>194852695.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1059.506</t>
+          <t>1354.063</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-24.52</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>65.2</v>
+        <v>65.83</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.76</v>
+        <v>59.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-35.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70672129.0</t>
+          <t>91855404.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>51050573.6</v>
+        <v>55760487</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>67636417.9</t>
+          <t>61976845.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>49798402.58</v>
+        <v>51320392.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-16585844</t>
+          <t>-6216358</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2577082.57131422</t>
+          <t>1221797.505564946</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-9131267.9503759</t>
+          <t>-6232270.356056064</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>70672129.0</t>
+          <t>91855404.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>19.40</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>486.403</t>
+          <t>1059.506</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-24.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.08</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>64.58</v>
+        <v>65.2</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.44</v>
+        <v>58.76</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.22</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.99</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-30.95</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>48728972.4</v>
+        <v>51050573.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>81984528.8</t>
+          <t>67636417.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>48567572.86</v>
+        <v>49798402.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-33255556</t>
+          <t>-16585844</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4705873.575257879</t>
+          <t>2577082.57131422</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-10676939.76546222</t>
+          <t>-9131267.9503759</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>19.40</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>484.079</t>
+          <t>486.403</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,92 +6488,92 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-40.56</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-47.44</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,17 +6604,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>64.09999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.15</v>
+        <v>58.44</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-28.19</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>53378696</v>
+        <v>48728972.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>101549205.5</t>
+          <t>81984528.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>48028060.24</v>
+        <v>48567572.86</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-48170509</t>
+          <t>-33255556</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>7502748.728116079</t>
+          <t>4705873.575257879</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-8338053.473961905</t>
+          <t>-10676939.76546222</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>800.087</t>
+          <t>484.079</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,22 +6928,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,219 +7034,219 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>63.52</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>57.84</v>
+        <v>58.15</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>56.89</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-28.19</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>163091312.6356534</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>53378696</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>101549205.5</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>48028060.24</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-48170509</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>7502748.728116079</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-8338053.473961905</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-26.41</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>163127312.9295875</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>62471906.6</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>121358388.6</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>47556857.96</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-58886481</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>10382894.58303935</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-4720287.39774853</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>4.47</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN17" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,68 +7894,68 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN18" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1177.447</t>
+          <t>1151.287</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,141 +9184,141 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>57.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>68.92</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>60.56</v>
+        <v>61.16</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.31</v>
+        <v>56.6</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>23.41</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-29.75</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>163091312.6356534</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>149719715</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>157079528.3</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>44057108.44</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-7359813</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>20657543.88911799</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>13651562.01972742</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>163127312.9295875</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>180244870.6</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>161062192.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>42670813.98</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>19182677</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>21931358.77446173</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>21289870.83132054</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>81097612.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="BG21" t="inlineStr">
         <is>
           <t>2025/10/22</t>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2189.997</t>
+          <t>1177.447</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>59.93</v>
+        <v>60.56</v>
       </c>
       <c r="AN22" t="n">
-        <v>55.99</v>
+        <v>56.31</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>43.70</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>204266767.4</v>
+        <v>180244870.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>153514394.7</t>
+          <t>161062192.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>41211816.88</v>
+        <v>42670813.98</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>50752372</t>
+          <t>19182677</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>22047992.94594195</t>
+          <t>21931358.77446173</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>31051352.88962071</t>
+          <t>21289870.83132054</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>148451128.0</t>
+          <t>81097612.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>22.60</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3083.64</t>
+          <t>2189.997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>68.47999999999999</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>59.37</v>
+        <v>59.93</v>
       </c>
       <c r="AN23" t="n">
-        <v>55.7</v>
+        <v>55.99</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>43.70</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-46.13</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>163127312.9295875</t>
+          <t>163091312.6356534</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>196536229.2</v>
+        <v>204266767.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>140950400.0</t>
+          <t>153514394.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>38471387.22</v>
+        <v>41211816.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>55585829</t>
+          <t>50752372</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20411018.41072763</t>
+          <t>22047992.94594195</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>36670902.22684878</t>
+          <t>31051352.88962071</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>214153238.0</t>
+          <t>148451128.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電網維運.xlsx
+++ b/Result/checksun_type/電網維運.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>646.583</t>
+          <t>516.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,22 +1029,22 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.62</v>
+        <v>101.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.76</v>
+        <v>104.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.97</t>
+          <t>104.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.78</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>66712202.0</t>
+          <t>53428345.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>104630422.2</v>
+        <v>90868663.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>110389018.3</t>
+          <t>101082315.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>197447365.46</v>
+        <v>193362855.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5758596</t>
+          <t>-10213652</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-18182772.10497662</t>
+          <t>-19246839.43340649</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-23115132.73890021</t>
+          <t>-25099209.73977077</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>66712202.0</t>
+          <t>53428345.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1181.443</t>
+          <t>646.583</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.74</v>
+        <v>101.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>104.83</v>
+        <v>104.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>105.04</t>
+          <t>104.97</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.64</t>
+          <t>-131.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>111924097.6</v>
+        <v>104630422.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>123203067.6</t>
+          <t>110389018.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>200134642.08</v>
+        <v>197447365.46</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-11278970</t>
+          <t>-5758596</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17285979.26244506</t>
+          <t>-18182772.10497662</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-20878466.96126726</t>
+          <t>-23115132.73890021</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1520.716</t>
+          <t>1181.443</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>101.8</v>
+        <v>101.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>104.86</v>
+        <v>104.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>105.12</t>
+          <t>105.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.11</t>
+          <t>-134.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>103202924</v>
+        <v>111924097.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>132882164.3</t>
+          <t>123203067.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>201053456.9</v>
+        <v>200134642.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-29679240</t>
+          <t>-11278970</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16632799.68084102</t>
+          <t>-17285979.26244506</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-22826205.88746065</t>
+          <t>-20878466.96126726</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>550.832</t>
+          <t>1520.716</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.29</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.87</t>
+          <t>96.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.68</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>102.14</v>
+        <v>101.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>104.91</v>
+        <v>104.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.22</t>
+          <t>105.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.87</t>
+          <t>-137.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>99209604.59999999</v>
+        <v>103202924</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>160755783.9</t>
+          <t>132882164.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>200342843.58</v>
+        <v>201053456.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-61546179</t>
+          <t>-29679240</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-15506725.825092</t>
+          <t>-16632799.68084102</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-28477904.92889903</t>
+          <t>-22826205.88746065</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>102.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,33 +3204,33 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN7" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3594,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,33 +3634,33 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1459.14</t>
+          <t>1183.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>104.8</v>
+        <v>104.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.6</v>
+        <v>105.44</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>105.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-52.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.49</t>
+          <t>-131.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>240594220.2</v>
+        <v>222301963.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>198554746.8</t>
+          <t>191158060.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>221461486.3</v>
+        <v>220229469.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>42039473</t>
+          <t>31143902</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-683525.8033344564</t>
+          <t>-3021017.166017586</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9428202.435408056</t>
+          <t>-15877219.6607748</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>146495369.0</t>
+          <t>116900919.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1985.218</t>
+          <t>1459.14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>105.28</v>
+        <v>104.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>105.69</v>
+        <v>105.6</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-94.00</t>
+          <t>-63.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.11</t>
+          <t>-127.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>343357662.2109375</t>
+          <t>342984307.3957447</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>236949826.2</v>
+        <v>240594220.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>211794368.0</t>
+          <t>198554746.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>221171326.8</v>
+        <v>221461486.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>25155458</t>
+          <t>42039473</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>906415.4024971072</t>
+          <t>-683525.8033344564</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3049433.097905278</t>
+          <t>-9428202.435408056</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>194852695.0</t>
+          <t>146495369.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1354.063</t>
+          <t>1834.972</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>65.83</v>
+        <v>66.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>59.08</v>
+        <v>59.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-23.79</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-35.72</t>
+          <t>-39.33</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>163091312.6356534</t>
+          <t>163115023.0829787</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>91855404.0</t>
+          <t>119871452.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>55760487</v>
+        <v>69236552.40000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>61976845.5</t>
+          <t>65854229.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>51320392.56</v>
+        <v>53421696.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6216358</t>
+          <t>3382322</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1221797.505564946</t>
+          <t>734449.9383809876</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6232270.356056064</t>
+          <t>-1945961.681130782</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>91855404.0</t>
+          <t>119871452.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1059.506</t>
+          <t>1354.063</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-24.52</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM14" t